--- a/Data/EXCEL/Transfer/salemon/20240711/6555-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6555-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{20EFE4CD-6DFE-4549-9246-210C22170757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{711E9024-F46E-4535-B5F1-93F7EA221168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{B363499D-2606-4DBA-A0B0-449FEC3BDAEB}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{AE69C3E9-32F6-4BEA-912E-977EEF19F677}"/>
   </bookViews>
   <sheets>
     <sheet name="6555-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,20 +1261,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89E5154C-1AA5-4320-B7BF-95C6D1441D9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CDA611-7069-4098-B619-F6FA473860E6}">
   <dimension ref="A1:Q224"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1301,7 +1301,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1383,7 +1383,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1422,7 +1422,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>-34.200000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>-36.1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>-41.2</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>-36.6</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>-27.3</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>-61.6</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>-62.4</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>-61.7</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>-63.1</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>-64.599999999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>-66.599999999999994</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>-65.2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>-63.9</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>-61.2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>-66.599999999999994</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>-70.7</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>-80.900000000000006</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>69.400000000000006</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>72.8</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>70.400000000000006</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>78.099999999999994</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>70.5</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>79.400000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>63.1</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2906,7 +2906,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>95.6</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>88.8</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>34.200000000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>42.2</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>65.8</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>44317</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>65.3</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>76.900000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>44256</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>107.4</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>158.6</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>44197</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>145.80000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>-11.8</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>44136</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>-13.8</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>44075</v>
       </c>
@@ -3860,7 +3860,7 @@
         <v>-17.3</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>-17.899999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>44013</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>-15.6</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4019,7 +4019,7 @@
         <v>-18.3</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>43952</v>
       </c>
@@ -4072,7 +4072,7 @@
         <v>-24.2</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>-21.8</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>43891</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>-33.6</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>-48.6</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>43831</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>-43.9</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>30.9</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>43770</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="10">
         <v>43709</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>40.700000000000003</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4549,7 +4549,7 @@
         <v>38.6</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="10">
         <v>43647</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>39.200000000000003</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>43.4</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="10">
         <v>43586</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>47.2</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>44.4</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="10">
         <v>43525</v>
       </c>
@@ -4814,7 +4814,7 @@
         <v>37.299999999999997</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="10">
         <v>43466</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="10">
         <v>43405</v>
       </c>
@@ -5026,7 +5026,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="10">
         <v>43344</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="10">
         <v>43282</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5291,7 +5291,7 @@
         <v>9.23</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="10">
         <v>43221</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5397,7 +5397,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="10">
         <v>43160</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="10">
         <v>43101</v>
       </c>
@@ -5556,7 +5556,7 @@
         <v>101.5</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5609,7 +5609,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="10">
         <v>43040</v>
       </c>
@@ -5662,7 +5662,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="10">
         <v>42979</v>
       </c>
@@ -5768,7 +5768,7 @@
         <v>9.33</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5821,7 +5821,7 @@
         <v>8.1199999999999992</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="10">
         <v>42917</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>42887</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="10">
         <v>42856</v>
       </c>
@@ -5980,7 +5980,7 @@
         <v>-3.18</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>42826</v>
       </c>
@@ -6033,7 +6033,7 @@
         <v>-12.1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="10">
         <v>42795</v>
       </c>
@@ -6086,7 +6086,7 @@
         <v>-9.33</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>42767</v>
       </c>
@@ -6139,7 +6139,7 @@
         <v>-6.73</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="10">
         <v>42736</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>-38.200000000000003</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>42705</v>
       </c>
@@ -6245,7 +6245,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="10">
         <v>42675</v>
       </c>
@@ -6298,7 +6298,7 @@
         <v>42.8</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>42644</v>
       </c>
@@ -6351,7 +6351,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="10">
         <v>42614</v>
       </c>
@@ -6404,7 +6404,7 @@
         <v>57.3</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>42583</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>64.900000000000006</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="10">
         <v>42552</v>
       </c>
@@ -6510,7 +6510,7 @@
         <v>68.400000000000006</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>42522</v>
       </c>
@@ -6563,7 +6563,7 @@
         <v>80.2</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="10">
         <v>42491</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>95.8</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>42461</v>
       </c>
@@ -6669,7 +6669,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="10">
         <v>42430</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v>90.6</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>42401</v>
       </c>
@@ -6775,7 +6775,7 @@
         <v>99.6</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="10">
         <v>42370</v>
       </c>
@@ -6828,7 +6828,7 @@
         <v>63.1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>42339</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>57.9</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="10">
         <v>42309</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>42278</v>
       </c>
@@ -6987,7 +6987,7 @@
         <v>42.9</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="10">
         <v>42248</v>
       </c>
@@ -7040,7 +7040,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>42217</v>
       </c>
@@ -7093,567 +7093,567 @@
         <v>34.200000000000003</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="10">
         <v>44317</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="10">
         <v>44256</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="10">
         <v>44197</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="10">
         <v>44136</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A160" s="10">
         <v>44075</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A162" s="10">
         <v>44013</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A164" s="10">
         <v>43952</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A166" s="10">
         <v>43891</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A168" s="10">
         <v>43831</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A170" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A171" s="10">
         <v>43770</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A172" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A173" s="10">
         <v>43709</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A174" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A175" s="10">
         <v>43647</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A176" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A177" s="10">
         <v>43586</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A178" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A179" s="10">
         <v>43525</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A180" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A181" s="10">
         <v>43466</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A182" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A183" s="10">
         <v>43405</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A184" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A185" s="10">
         <v>43344</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A186" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A187" s="10">
         <v>43282</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A189" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A190" s="10">
         <v>43221</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A191" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A192" s="10">
         <v>43160</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A193" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A194" s="10">
         <v>43101</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A195" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A196" s="10">
         <v>43040</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A197" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A198" s="10">
         <v>42979</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A199" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A200" s="10">
         <v>42917</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A201" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A202" s="10">
         <v>42856</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A203" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A204" s="10">
         <v>42795</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A205" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A206" s="10">
         <v>42736</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A208" s="5">
         <v>42705</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A209" s="10">
         <v>42675</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A210" s="5">
         <v>42644</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A211" s="10">
         <v>42614</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A212" s="5">
         <v>42583</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A213" s="10">
         <v>42552</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A214" s="5">
         <v>42522</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A215" s="10">
         <v>42491</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A216" s="5">
         <v>42461</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A217" s="10">
         <v>42430</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A218" s="5">
         <v>42401</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A219" s="10">
         <v>42370</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A220" s="5">
         <v>42339</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A221" s="10">
         <v>42309</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A222" s="5">
         <v>42278</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A223" s="10">
         <v>42248</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A224" s="5">
         <v>42217</v>
       </c>
